--- a/data/processed/crypto_jobs_clean_v1.xlsx
+++ b/data/processed/crypto_jobs_clean_v1.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="jobs_master" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="jobs_view" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="jobs_text" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="manual_review" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="active_near_fit" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="applications" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="skills_gap" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="skill_recommendations" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs_master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs_view" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs_text" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="manual_review" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="applications" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills_gap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_recommendations" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="active_near_fit" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1083,90 +1083,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>decision</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>city_region</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>work_mode</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>seniority_manual</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>main_reason</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>review_notes</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1233,7 +1149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1271,7 +1187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1341,4 +1257,88 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>city_region</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>work_mode</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>seniority_manual</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>main_reason</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>review_notes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/processed/crypto_jobs_clean_v1.xlsx
+++ b/data/processed/crypto_jobs_clean_v1.xlsx
@@ -7,14 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs_master" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs_view" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs_text" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="manual_review" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="applications" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills_gap" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_recommendations" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="active_near_fit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="active_near_fit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="applications" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="manual_review" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs_master" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills_gap" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_recommendations" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,6 +427,354 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>salary</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>salary_usd_equivalent</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>work_mode</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>city_region</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>seniority_manual</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>main_reason</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>review_notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_sent</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>review_verdict</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>pdf_ready</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>date_added</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>city_region</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>contract_type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>job_category</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>role_family</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>seniority</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>personal_fit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>should_be_filtered</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>french_required</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>language_notes</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>work_mode</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>location_fit</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>seniority_manual</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>coding_intensity</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>experience_fit</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>main_reason</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>review_notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -639,517 +985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>job_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>city_region</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>work_format</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>salary</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>salary_usd_equivalent</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>contract_type</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>availability_status</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>date_published</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>job_category</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>role_family</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>seniority</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>skills_all</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>required_skills</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>preferred_skills</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>fit_score</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>job_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>full_text</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>role_family</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>role_subcategory</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>seniority</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>years_experience_min</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>years_experience_max</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>skills_all</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>required_skills</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>preferred_skills</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>analysis_note</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>fit_score</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>fit_reasoning</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>job_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>city_region</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>contract_type</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>job_category</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>role_family</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>seniority</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>personal_fit</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>decision</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>should_be_filtered</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>french_required</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>language_notes</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>work_mode</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>location_fit</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>seniority_manual</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>coding_intensity</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>experience_fit</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>main_reason</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>review_notes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>job_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>review_verdict</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>pdf_ready</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>date_added</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1187,7 +1023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1257,88 +1093,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>decision</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>city_region</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>work_mode</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>seniority_manual</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>main_reason</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>review_notes</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/processed/crypto_jobs_clean_v1.xlsx
+++ b/data/processed/crypto_jobs_clean_v1.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -440,11 +440,12 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,25 +501,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>also_on</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>seniority_manual</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>main_reason</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>review_notes</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>job_id</t>
         </is>
@@ -613,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -627,19 +633,20 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
     <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,65 +707,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>duplicate_group</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>personal_fit</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>decision</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>applied</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>should_be_filtered</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>french_required</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>language_notes</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>work_mode</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>location_fit</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>seniority_manual</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>coding_intensity</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>experience_fit</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>main_reason</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>review_notes</t>
         </is>
@@ -775,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -811,6 +823,7 @@
     <col width="15" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -977,6 +990,11 @@
       <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>fit_reasoning</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>duplicate_group</t>
         </is>
       </c>
     </row>

--- a/data/processed/crypto_jobs_clean_v1.xlsx
+++ b/data/processed/crypto_jobs_clean_v1.xlsx
@@ -541,19 +541,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,35 +578,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>date_sent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>days_from_published</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>days_from_found</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>date_published</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>review_verdict</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>pdf_ready</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>date_added</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>job_id</t>
         </is>
